--- a/STI/CellularAutomata/img/PSNR.xlsx
+++ b/STI/CellularAutomata/img/PSNR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Julia Ihrenberger\Documents\1_Studium_Informatik\informational-mastery\STI\CellularAutomata\img\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD78FDCC-2258-4D32-A31D-9CF4AE14404B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB407C9-BC81-4A09-84CB-63DD2CD1AA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26115" yWindow="2640" windowWidth="21600" windowHeight="11505" activeTab="1" xr2:uid="{13250463-45F0-42CA-BC09-080EAC51F337}"/>
+    <workbookView xWindow="4080" yWindow="2730" windowWidth="21600" windowHeight="11505" xr2:uid="{13250463-45F0-42CA-BC09-080EAC51F337}"/>
   </bookViews>
   <sheets>
     <sheet name="PSNR" sheetId="1" r:id="rId1"/>
@@ -596,7 +596,7 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>28.45</v>

--- a/STI/CellularAutomata/img/PSNR.xlsx
+++ b/STI/CellularAutomata/img/PSNR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Julia Ihrenberger\Documents\1_Studium_Informatik\informational-mastery\STI\CellularAutomata\img\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jihre\Documents\1_INF_M\informational-mastery\STI\CellularAutomata\img\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB407C9-BC81-4A09-84CB-63DD2CD1AA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E3AE38-E842-4041-9D2E-3DDF357AB354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="2730" windowWidth="21600" windowHeight="11505" xr2:uid="{13250463-45F0-42CA-BC09-080EAC51F337}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{13250463-45F0-42CA-BC09-080EAC51F337}"/>
   </bookViews>
   <sheets>
     <sheet name="PSNR" sheetId="1" r:id="rId1"/>
@@ -767,66 +767,66 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0.9889</v>
+        <v>0.98919999999999997</v>
       </c>
       <c r="E3">
-        <v>0.97650000000000003</v>
+        <v>0.97719999999999996</v>
       </c>
       <c r="G3">
-        <v>0.96319999999999995</v>
+        <v>0.9637</v>
       </c>
       <c r="I3">
-        <v>0.94689999999999996</v>
+        <v>0.94869999999999999</v>
       </c>
       <c r="K3">
-        <v>0.92700000000000005</v>
+        <v>0.93089999999999995</v>
       </c>
       <c r="M3">
-        <v>0.89980000000000004</v>
+        <v>0.90859999999999996</v>
       </c>
       <c r="O3">
-        <v>0.86339999999999995</v>
+        <v>0.87860000000000005</v>
       </c>
       <c r="Q3">
-        <v>0.80569999999999997</v>
+        <v>0.82979999999999998</v>
       </c>
       <c r="S3">
-        <v>0.70630000000000004</v>
+        <v>0.72940000000000005</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>0.98919999999999997</v>
+        <v>0.9889</v>
       </c>
       <c r="E4">
-        <v>0.97719999999999996</v>
+        <v>0.97650000000000003</v>
       </c>
       <c r="G4">
-        <v>0.9637</v>
+        <v>0.96319999999999995</v>
       </c>
       <c r="I4">
-        <v>0.94869999999999999</v>
+        <v>0.94689999999999996</v>
       </c>
       <c r="K4">
-        <v>0.93089999999999995</v>
+        <v>0.92700000000000005</v>
       </c>
       <c r="M4">
-        <v>0.90859999999999996</v>
+        <v>0.89980000000000004</v>
       </c>
       <c r="O4">
-        <v>0.87860000000000005</v>
+        <v>0.86339999999999995</v>
       </c>
       <c r="Q4">
-        <v>0.82979999999999998</v>
+        <v>0.80569999999999997</v>
       </c>
       <c r="S4">
-        <v>0.72940000000000005</v>
+        <v>0.70630000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
